--- a/hardware/pid-temperature-controller-hardware.xlsx
+++ b/hardware/pid-temperature-controller-hardware.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30126"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{052C4E1F-53FD-4711-9922-A62D9336D4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{433B8BC9-53C3-462D-BECF-4F4D570A2B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t>Component</t>
   </si>
@@ -91,6 +91,12 @@
   </si>
   <si>
     <t>Epoxy sealed</t>
+  </si>
+  <si>
+    <t>Capasitor [C1]</t>
+  </si>
+  <si>
+    <t>Ceramic; 100nF</t>
   </si>
   <si>
     <t>Power Supply</t>
@@ -543,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.28515625" customWidth="1"/>
@@ -674,9 +680,7 @@
       <c r="C9" s="3">
         <v>1</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
@@ -697,10 +701,10 @@
         <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="3" t="s">
         <v>25</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>6</v>
@@ -711,12 +715,26 @@
         <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="3">
-        <v>1</v>
-      </c>
       <c r="D12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/hardware/pid-temperature-controller-hardware.xlsx
+++ b/hardware/pid-temperature-controller-hardware.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30126"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{433B8BC9-53C3-462D-BECF-4F4D570A2B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A7DD5A5-1C64-4DB4-BC6B-1646F62BD37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t>Component</t>
   </si>
@@ -93,7 +93,7 @@
     <t>Epoxy sealed</t>
   </si>
   <si>
-    <t>Capasitor [C1]</t>
+    <t>Capacitor [C1]</t>
   </si>
   <si>
     <t>Ceramic; 100nF</t>
@@ -680,7 +680,9 @@
       <c r="C9" s="3">
         <v>1</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
